--- a/artfynd/A 2823-2021 artfynd.xlsx
+++ b/artfynd/A 2823-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2823-2021 artfynd.xlsx
+++ b/artfynd/A 2823-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2039,6 +2039,231 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128464161</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91654</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>658</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svedjorna, Svedjorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>623309</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6957880</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Grov granlåga</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128464160</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91323</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svedjorna, Svedjorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>623283</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6957791</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2823-2021 artfynd.xlsx
+++ b/artfynd/A 2823-2021 artfynd.xlsx
@@ -2044,7 +2044,7 @@
         <v>128464161</v>
       </c>
       <c r="B13" t="n">
-        <v>91654</v>
+        <v>91656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>128464160</v>
       </c>
       <c r="B14" t="n">
-        <v>91323</v>
+        <v>91325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 2823-2021 artfynd.xlsx
+++ b/artfynd/A 2823-2021 artfynd.xlsx
@@ -2044,7 +2044,7 @@
         <v>128464161</v>
       </c>
       <c r="B13" t="n">
-        <v>91656</v>
+        <v>91748</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>128464160</v>
       </c>
       <c r="B14" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 2823-2021 artfynd.xlsx
+++ b/artfynd/A 2823-2021 artfynd.xlsx
@@ -2044,7 +2044,7 @@
         <v>128464161</v>
       </c>
       <c r="B13" t="n">
-        <v>91748</v>
+        <v>91754</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>128464160</v>
       </c>
       <c r="B14" t="n">
-        <v>91417</v>
+        <v>91423</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 2823-2021 artfynd.xlsx
+++ b/artfynd/A 2823-2021 artfynd.xlsx
@@ -2044,7 +2044,7 @@
         <v>128464161</v>
       </c>
       <c r="B13" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>128464160</v>
       </c>
       <c r="B14" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 2823-2021 artfynd.xlsx
+++ b/artfynd/A 2823-2021 artfynd.xlsx
@@ -2044,7 +2044,7 @@
         <v>128464161</v>
       </c>
       <c r="B13" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>128464160</v>
       </c>
       <c r="B14" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 2823-2021 artfynd.xlsx
+++ b/artfynd/A 2823-2021 artfynd.xlsx
@@ -2044,7 +2044,7 @@
         <v>128464161</v>
       </c>
       <c r="B13" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>128464160</v>
       </c>
       <c r="B14" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 2823-2021 artfynd.xlsx
+++ b/artfynd/A 2823-2021 artfynd.xlsx
@@ -2044,7 +2044,7 @@
         <v>128464161</v>
       </c>
       <c r="B13" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>128464160</v>
       </c>
       <c r="B14" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 2823-2021 artfynd.xlsx
+++ b/artfynd/A 2823-2021 artfynd.xlsx
@@ -2044,7 +2044,7 @@
         <v>128464161</v>
       </c>
       <c r="B13" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>128464160</v>
       </c>
       <c r="B14" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 2823-2021 artfynd.xlsx
+++ b/artfynd/A 2823-2021 artfynd.xlsx
@@ -2044,7 +2044,7 @@
         <v>128464161</v>
       </c>
       <c r="B13" t="n">
-        <v>91795</v>
+        <v>91800</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>128464160</v>
       </c>
       <c r="B14" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 2823-2021 artfynd.xlsx
+++ b/artfynd/A 2823-2021 artfynd.xlsx
@@ -2044,7 +2044,7 @@
         <v>128464161</v>
       </c>
       <c r="B13" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>128464160</v>
       </c>
       <c r="B14" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 2823-2021 artfynd.xlsx
+++ b/artfynd/A 2823-2021 artfynd.xlsx
@@ -2044,7 +2044,7 @@
         <v>128464161</v>
       </c>
       <c r="B13" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>128464160</v>
       </c>
       <c r="B14" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
